--- a/samples/official-attendance/beacon_official_sheet_sample.xlsx
+++ b/samples/official-attendance/beacon_official_sheet_sample.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>샘플가온</t>
+          <t>신민준</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>961220-1******</t>
+          <t>011015-1******</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>샘플나래</t>
+          <t>오서연</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>971112-1******</t>
+          <t>991227-1******</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -837,12 +837,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>샘플다솜</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>991227-1******</t>
+          <t>010624-1******</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>샘플라온</t>
+          <t>임하윤</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>901212-1******</t>
+          <t>030922-1******</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>샘플마루</t>
+          <t>조도현</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>011221-1******</t>
+          <t>981110-1******</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>샘플바다</t>
+          <t>이수아</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>940922-1******</t>
+          <t>951226-1******</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -1122,7 +1122,7 @@
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>샘플사랑</t>
+          <t>한예준</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>930921-1******</t>
+          <t>930226-1******</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>샘플아름</t>
+          <t>안지우</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>940112-1******</t>
+          <t>950516-1******</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>샘플자람</t>
+          <t>권건우</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>010311-1******</t>
+          <t>900828-1******</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>샘플차오</t>
+          <t>박서윤</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>930226-1******</t>
+          <t>930911-1******</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>샘플카이</t>
+          <t>윤현우</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>020217-1******</t>
+          <t>980706-1******</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -1547,29 +1547,29 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
           <t>○</t>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>샘플타온</t>
+          <t>전지안</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>950516-1******</t>
+          <t>920502-1******</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -1632,52 +1632,52 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>샘플하늘</t>
+          <t>서우진</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>040802-1******</t>
+          <t>041105-1******</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>샘플고운</t>
+          <t>황하은</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>971203-1******</t>
+          <t>010828-1******</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -1802,7 +1802,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>샘플나빛</t>
+          <t>송선우</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>930911-1******</t>
+          <t>910216-1******</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>샘플다온</t>
+          <t>한다은</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>930913-1******</t>
+          <t>040828-1******</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -1972,7 +1972,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>샘플라희</t>
+          <t>임시우</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>040328-1******</t>
+          <t>950209-1******</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>샘플모아</t>
+          <t>황유진</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>041005-1******</t>
+          <t>980223-1******</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -2142,7 +2142,7 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>샘플보람</t>
+          <t>이주원</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>940113-1******</t>
+          <t>040113-1******</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>샘플소담</t>
+          <t>박채원</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>041105-1******</t>
+          <t>001025-1******</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -2312,7 +2312,7 @@
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>샘플여울</t>
+          <t>송지훈</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>971215-1******</t>
+          <t>901209-1******</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -2397,7 +2397,7 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>샘플이든</t>
+          <t>황나은</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>030904-1******</t>
+          <t>940620-1******</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>샘플준서</t>
+          <t>송승현</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>910811-1******</t>
+          <t>020523-1******</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>×</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>샘플지안</t>
+          <t>정소율</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>040828-1******</t>
+          <t>980605-1******</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>샘플채원</t>
+          <t>이태윤</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>940603-1******</t>
+          <t>950409-1******</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>샘플하율</t>
+          <t>신아린</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>940817-1******</t>
+          <t>961221-1******</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>샘플해솔</t>
+          <t>한재윤</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>030223-1******</t>
+          <t>951116-1******</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>샘플휘온</t>
+          <t>황가영</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>900113-1******</t>
+          <t>020518-1******</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>샘플누리</t>
+          <t>서동현</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>911120-1******</t>
+          <t>920304-1******</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>샘플새봄</t>
+          <t>권보라</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>020901-1******</t>
+          <t>980604-1******</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">

--- a/samples/official-attendance/beacon_official_sheet_sample.xlsx
+++ b/samples/official-attendance/beacon_official_sheet_sample.xlsx
@@ -1026,10 +1026,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1122,52 +1122,52 @@
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>×</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
           <t>▦15</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1292,27 +1292,27 @@
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>▦15</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>◎</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1467,32 +1467,32 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>▦15</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
           <t>○</t>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>○</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -1722,29 +1722,29 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>▦15</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
           <t>○</t>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>▲</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
     </row>
@@ -1791,10 +1791,10 @@
         <v>10</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
@@ -1802,17 +1802,17 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
@@ -1972,14 +1972,14 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
           <t>○</t>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2142,42 +2142,42 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>▦15</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>▦15</t>
+          <t>○</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>▦15</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2397,42 +2397,42 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>▲</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -2471,10 +2471,10 @@
         <v>10</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
@@ -2482,7 +2482,7 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         <v>10</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2641,10 +2641,10 @@
         <v>10</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
@@ -2652,7 +2652,7 @@
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2742,42 +2742,42 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>◎</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
